--- a/one up/普物實驗/Lab12 熱功當量/E24146107_王翊權_預報12_表格.xlsx
+++ b/one up/普物實驗/Lab12 熱功當量/E24146107_王翊權_預報12_表格.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\school\one up\普物實驗\Lab12 熱功當量\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D00777FC-FF38-44D8-B708-EB971B3DBBB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8F21C7A-5473-45A0-A439-04D3329B06F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{F223CEAA-A9E0-4970-A5DD-753DA0C12824}"/>
+    <workbookView minimized="1" xWindow="4608" yWindow="3192" windowWidth="13824" windowHeight="8376" xr2:uid="{F223CEAA-A9E0-4970-A5DD-753DA0C12824}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
   <si>
     <t>T_0</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -105,6 +105,22 @@
   </si>
   <si>
     <t>g</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>=</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -188,12 +204,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
@@ -201,11 +214,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -542,87 +555,115 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C3484B5-FB18-4C3E-9A11-3865AFCC3A47}">
   <dimension ref="B1:E13"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4"/>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="4"/>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B4" s="3" t="s">
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B2" s="1">
+        <v>24.5</v>
+      </c>
+      <c r="C2" s="1">
+        <v>250.8</v>
+      </c>
+      <c r="D2" s="1">
+        <f>0.05*C2+10</f>
+        <v>22.54</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B8" s="1" t="s">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B5" s="1">
+        <f>C2+C5</f>
+        <v>510.8</v>
+      </c>
+      <c r="C5" s="1">
+        <v>260</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1.339</v>
+      </c>
+      <c r="E5" s="1">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B9" s="1"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B10" s="2" t="s">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="4"/>
+      <c r="C9" s="1">
+        <v>19.5</v>
+      </c>
+      <c r="D9" s="1">
+        <v>24.5</v>
+      </c>
+      <c r="E9" s="1">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B12" s="2" t="s">
+      <c r="C10" s="1">
+        <v>950</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1240</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B13" s="2"/>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -635,56 +676,101 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F84A345-E81B-4D1E-A387-EF35254C2657}">
-  <dimension ref="B3:F8"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <dimension ref="B1:L8"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B3" s="2" t="s">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B2">
+        <v>1.3380000000000001</v>
+      </c>
+      <c r="C2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
         <v>240</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <v>260</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>280</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="1">
         <v>300</v>
       </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B4" s="1" t="s">
+      <c r="H3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B7" s="2" t="s">
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="H4" s="1">
+        <v>240</v>
+      </c>
+      <c r="I4" s="4"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="I5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="I3:I4"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="D4:D5"/>
@@ -699,23 +785,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5F86472-5DA5-482B-8471-AB8BF91009A5}">
   <dimension ref="B3:D4"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B3" s="2" t="s">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
